--- a/sample-data/northfield/northfield-college.xlsx
+++ b/sample-data/northfield/northfield-college.xlsx
@@ -4,11 +4,12 @@
   <sheets>
     <sheet name="Time structure" sheetId="1" r:id="rId1"/>
     <sheet name="Departments" sheetId="2" r:id="rId2"/>
-    <sheet name="Rooms" sheetId="3" r:id="rId3"/>
-    <sheet name="Subjects" sheetId="4" r:id="rId4"/>
-    <sheet name="Teachers" sheetId="5" r:id="rId5"/>
-    <sheet name="Sections" sheetId="6" r:id="rId6"/>
-    <sheet name="Assignments" sheetId="7" r:id="rId7"/>
+    <sheet name="Room types" sheetId="3" r:id="rId3"/>
+    <sheet name="Rooms" sheetId="4" r:id="rId4"/>
+    <sheet name="Subjects" sheetId="5" r:id="rId5"/>
+    <sheet name="Teachers" sheetId="6" r:id="rId6"/>
+    <sheet name="Sections" sheetId="7" r:id="rId7"/>
+    <sheet name="Assignments" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -53,43 +54,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">break_after</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>4</v>
+          <t xml:space="preserve">start_time</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">start_time</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:00</t>
-        </is>
+          <t xml:space="preserve">period_minutes</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">period_minutes</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>55</v>
+          <t xml:space="preserve">breaks</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2:10:Tea break;4:40:Lunch</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">break_minutes</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>40</v>
+          <t xml:space="preserve">day_periods</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sat:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blocked</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mon-1:Assembly;Wed-7:Sports</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -198,957 +215,115 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacity</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">department</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">facilities</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">events_only</t>
+          <t xml:space="preserve">used_for</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A-101</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>66</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector;Smart board</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lectures</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A-102</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>66</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">Lecture theatre</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lectures</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">A-103</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>66</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">Tutorial room</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lectures</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A-104</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>66</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector;Smart board</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">Computer lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A-201</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>66</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">Electronics lab</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">A-202</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>66</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector;Smart board</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">Mechanical lab</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B-101</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>66</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">Workshop</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B-102</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>66</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">Drawing hall</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">B-103</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>66</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector;Smart board</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C-101</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>66</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C-102</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>66</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lecture Theatre LT-1</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>120</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector;Sound system;Smart board</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lecture Theatre LT-2</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>120</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector;Sound system</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tutorial Room T-1</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>40</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">classroom</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Whiteboard</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Programming Lab 1</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>36</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Computers;Projector</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Programming Lab 2</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>36</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Computers;Projector</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Systems Lab</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>36</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Computers</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Networks Lab</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>36</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Computers;Network rack</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Web Technologies Lab</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>36</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Computers;Projector</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Database Lab</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>36</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Computers</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electronic Devices Lab</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>32</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oscilloscopes;Function generators</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital Electronics Lab</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>32</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trainer kits;Oscilloscopes</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Microprocessor Lab</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>32</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Computers;Trainer kits</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Communication Lab</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>32</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Signal generators;Spectrum analyser</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Strength of Materials Lab</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>36</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Universal testing machine</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing Workshop</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>40</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lathes;Milling machine;CNC machine</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Drawing Hall</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>40</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Drafting tables</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thermal &amp; Heat Transfer Lab</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>36</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat exchangers</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fluid Mechanics Lab</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>36</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lab</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flow bench;Pumps</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Main Seminar Hall</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>180</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">seminar</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector;Sound system;Stage;Video recording</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conference Room</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>30</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">seminar</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector;Video conferencing</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auditorium</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>450</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">seminar</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projector;Sound system;Stage;Lighting</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">Seminar hall</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lectures</t>
         </is>
       </c>
     </row>
@@ -1162,917 +337,987 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">code</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">capacity</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lecture_hours</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lab_hours</t>
+          <t xml:space="preserve">department</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lab_sessions</t>
+          <t xml:space="preserve">facilities</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">department</t>
+          <t xml:space="preserve">events_only</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS301</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data Structures</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+          <t xml:space="preserve">A-101</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>66</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector;Smart board</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS302</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Object Oriented Programming</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
+          <t xml:space="preserve">A-102</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>66</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS303</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Discrete Mathematics</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+          <t xml:space="preserve">A-103</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>66</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS304</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Computer Architecture</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
+          <t xml:space="preserve">A-104</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>66</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector;Smart board</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS501</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operating Systems</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+          <t xml:space="preserve">A-201</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>66</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS502</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Database Management Systems</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
+          <t xml:space="preserve">A-202</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>66</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector;Smart board</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS503</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Computer Networks</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
+          <t xml:space="preserve">B-101</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>66</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS504</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Theory of Computation</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
+          <t xml:space="preserve">B-102</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>66</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS505</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software Engineering</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
+          <t xml:space="preserve">B-103</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>66</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector;Smart board</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT301</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data Structures &amp; Algorithms</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
+          <t xml:space="preserve">C-101</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>66</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT302</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Web Technologies</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
+          <t xml:space="preserve">C-102</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>66</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classroom</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT303</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Database Systems</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
+          <t xml:space="preserve">Lecture Theatre LT-1</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>120</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lecture theatre</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector;Sound system;Smart board</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT304</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Discrete Structures</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
+          <t xml:space="preserve">Lecture Theatre LT-2</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>120</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lecture theatre</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector;Sound system</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT501</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cloud Computing</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
+          <t xml:space="preserve">Tutorial Room T-1</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>40</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tutorial room</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Whiteboard</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT502</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data Communication &amp; Networks</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
+          <t xml:space="preserve">Tutorial Room T-2</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>40</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tutorial room</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Whiteboard</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT503</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software Testing</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
+          <t xml:space="preserve">Programming Lab 1</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>36</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computers;Projector</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT504</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data Mining</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
+          <t xml:space="preserve">Programming Lab 2</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>36</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computers;Projector</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">EC301</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electronic Devices &amp; Circuits</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
+          <t xml:space="preserve">Systems Lab</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>36</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computers</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">EC302</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital Electronics</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
+          <t xml:space="preserve">Networks Lab</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>36</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computers;Network rack</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">EC303</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Signals &amp; Systems</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
+          <t xml:space="preserve">Web Technologies Lab</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>36</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computers;Projector</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">EC304</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Network Analysis</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
+          <t xml:space="preserve">Database Lab</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>36</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computers</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">EC501</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Microprocessors &amp; Microcontrollers</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
+          <t xml:space="preserve">Electronic Devices Lab</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>32</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electronics lab</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscilloscopes;Function generators</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">EC502</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analog &amp; Digital Communication</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
+          <t xml:space="preserve">Digital Electronics Lab</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>32</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electronics lab</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trainer kits;Oscilloscopes</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">EC503</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control Systems</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
+          <t xml:space="preserve">Microprocessor Lab</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>32</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electronics lab</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computers;Trainer kits</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">EC504</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electromagnetic Waves</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
+          <t xml:space="preserve">Communication Lab</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>32</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electronics lab</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Signal generators;Spectrum analyser</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME301</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Strength of Materials</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27">
-        <v>2</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
+          <t xml:space="preserve">Strength of Materials Lab</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>36</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical lab</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Universal testing machine</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME302</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering Thermodynamics</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
+          <t xml:space="preserve">Thermal &amp; Heat Transfer Lab</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>36</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical lab</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat exchangers</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME303</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing Processes</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>3</v>
-      </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
+          <t xml:space="preserve">Fluid Mechanics Lab</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>36</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical lab</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flow bench;Pumps</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME304</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine Drawing</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
+          <t xml:space="preserve">Manufacturing Workshop</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>40</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workshop</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lathes;Milling machine;CNC machine</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME501</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Transfer</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
+          <t xml:space="preserve">Drawing Hall</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>40</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drawing hall</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drafting tables</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME502</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fluid Mechanics &amp; Machines</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32">
-        <v>2</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
+          <t xml:space="preserve">Main Seminar Hall</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>180</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seminar hall</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector;Sound system;Stage;Video recording</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME503</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dynamics of Machines</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
+          <t xml:space="preserve">Conference Room</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seminar hall</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector;Video conferencing</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME504</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Industrial Engineering</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
+          <t xml:space="preserve">Auditorium</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>450</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seminar hall</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector;Sound system;Stage;Lighting</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MA301</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering Mathematics III</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HU301</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Professional Communication</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HU501</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entrepreneurship &amp; Management</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HUM</t>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
@@ -2086,632 +1331,1298 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t xml:space="preserve">name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lecture_hours</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lecture_block</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tutorial_hours</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lab_hours</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lab_sessions</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">department</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">max_hours</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">can_teach</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unavailable</t>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lecture_room_type</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lecture_needs</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lab_room_type</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lab_needs</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Rajesh Kumar</t>
+          <t xml:space="preserve">CS301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Data Structures</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C2">
-        <v>14</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS301;CS504</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mon-1;Mon-2</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computers</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Neha Gupta</t>
+          <t xml:space="preserve">CS302</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Object Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C3">
-        <v>16</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS302;CS505</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prof. Amandeep Singh</t>
+          <t xml:space="preserve">CS303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discrete Mathematics</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>18</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS301;CS303</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sat-5;Sat-6;Sat-7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ms. Priya Sharma</t>
+          <t xml:space="preserve">CS304</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Computer Architecture</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C5">
-        <v>18</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS302;CS304</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projector</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Sandeep Bansal</t>
+          <t xml:space="preserve">CS501</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Operating Systems</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS501;CS503</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fri-6;Fri-7</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prof. Kavita Joshi</t>
+          <t xml:space="preserve">CS502</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Database Management Systems</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C7">
-        <v>16</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS502;CS505</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ms. Anjali Mehta</t>
+          <t xml:space="preserve">CS503</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Computer Networks</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS501;CS503</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Network rack</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ms. Simran Kaur</t>
+          <t xml:space="preserve">CS504</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Theory of Computation</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>18</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS303;CS304;CS504</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wed-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr. Rohit Verma</t>
+          <t xml:space="preserve">CS505</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Software Engineering</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t xml:space="preserve">CSE</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>20</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS301;CS302;CS501;CS502;CS503</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Harpreet Kaur</t>
+          <t xml:space="preserve">IT301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Data Structures &amp; Algorithms</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t xml:space="preserve">IT</t>
         </is>
       </c>
-      <c r="C11">
-        <v>16</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT301;IT304</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wed-6;Wed-7</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prof. Manish Arora</t>
+          <t xml:space="preserve">IT302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Web Technologies</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t xml:space="preserve">IT</t>
         </is>
       </c>
-      <c r="C12">
-        <v>16</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT302;IT501</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ms. Deepika Rana</t>
+          <t xml:space="preserve">IT303</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Database Systems</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t xml:space="preserve">IT</t>
         </is>
       </c>
-      <c r="C13">
-        <v>18</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT303;IT503</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sat-1;Sat-2</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr. Vivek Sood</t>
+          <t xml:space="preserve">IT304</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discrete Structures</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t xml:space="preserve">IT</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT302;IT502;IT504</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Sunil Mehra</t>
+          <t xml:space="preserve">IT501</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">Cloud Computing</t>
         </is>
       </c>
       <c r="C15">
-        <v>16</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EC301;EC303</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tue-1</t>
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prof. Ritu Malhotra</t>
+          <t xml:space="preserve">IT502</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">Data Communication &amp; Networks</t>
         </is>
       </c>
       <c r="C16">
-        <v>18</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EC302;EC304</t>
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer lab</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Gaurav Chawla</t>
+          <t xml:space="preserve">IT503</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">Software Testing</t>
         </is>
       </c>
       <c r="C17">
-        <v>16</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EC501;EC503</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fri-1;Fri-2</t>
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ms. Pallavi Sethi</t>
+          <t xml:space="preserve">IT504</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
+          <t xml:space="preserve">Data Mining</t>
         </is>
       </c>
       <c r="C18">
-        <v>18</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EC502;EC504;EC303</t>
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr. Harish Thakur</t>
+          <t xml:space="preserve">EC301</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Electronic Devices &amp; Circuits</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t xml:space="preserve">ECE</t>
         </is>
       </c>
-      <c r="C19">
-        <v>20</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EC301;EC302;EC501;EC502</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electronics lab</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oscilloscopes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Balwinder Singh</t>
+          <t xml:space="preserve">EC302</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">Digital Electronics</t>
         </is>
       </c>
       <c r="C20">
-        <v>16</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME301;ME503</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thu-6;Thu-7</t>
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electronics lab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prof. Anil Saini</t>
+          <t xml:space="preserve">EC303</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">Signals &amp; Systems</t>
         </is>
       </c>
       <c r="C21">
-        <v>16</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME302;ME501</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sat-1;Sat-2</t>
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr. Jaspreet Gill</t>
+          <t xml:space="preserve">EC304</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">Network Analysis</t>
         </is>
       </c>
       <c r="C22">
-        <v>18</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME303;ME304</t>
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Meenakshi Rao</t>
+          <t xml:space="preserve">EC501</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">Microprocessors &amp; Microcontrollers</t>
         </is>
       </c>
       <c r="C23">
-        <v>16</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME502;ME504</t>
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electronics lab</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trainer kits</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr. Tarun Bedi</t>
+          <t xml:space="preserve">EC502</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
+          <t xml:space="preserve">Analog &amp; Digital Communication</t>
         </is>
       </c>
       <c r="C24">
-        <v>20</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ME301;ME303;ME304;ME501;ME502</t>
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electronics lab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Sunita Rani</t>
+          <t xml:space="preserve">EC503</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">AS</t>
+          <t xml:space="preserve">Control Systems</t>
         </is>
       </c>
       <c r="C25">
-        <v>16</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MA301</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sat-5;Sat-6;Sat-7</t>
+        <v>3</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Arvind Kapoor</t>
+          <t xml:space="preserve">EC504</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">AS</t>
+          <t xml:space="preserve">Electromagnetic Waves</t>
         </is>
       </c>
       <c r="C26">
-        <v>16</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MA301</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mon-7</t>
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ms. Nidhi Bhatia</t>
+          <t xml:space="preserve">ME301</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUM</t>
+          <t xml:space="preserve">Strength of Materials</t>
         </is>
       </c>
       <c r="C27">
-        <v>14</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HU301;HU501</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thu-7</t>
+        <v>3</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical lab</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Universal testing machine</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr. Karan Malik</t>
+          <t xml:space="preserve">ME302</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engineering Thermodynamics</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME303</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manufacturing Processes</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME304</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine Drawing</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drawing hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME501</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Transfer</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical lab</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat exchangers</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME502</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fluid Mechanics &amp; Machines</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical lab</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flow bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME503</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dynamics of Machines</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME504</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial Engineering</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MA301</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering Mathematics III</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HU301</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professional Communication</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t xml:space="preserve">HUM</t>
         </is>
       </c>
-      <c r="C28">
-        <v>14</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HU301;HU501</t>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HU501</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entrepreneurship &amp; Management</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUM</t>
         </is>
       </c>
     </row>
@@ -2735,29 +2646,29 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">semester</t>
+          <t xml:space="preserve">max_hours</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">students</t>
+          <t xml:space="preserve">max_per_day</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lab_groups</t>
+          <t xml:space="preserve">can_teach</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">group_names</t>
+          <t xml:space="preserve">unavailable</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE 3A</t>
+          <t xml:space="preserve">Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2765,27 +2676,27 @@
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3rd Sem</t>
-        </is>
+      <c r="C2">
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>60</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS301;CS504</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1;A2</t>
+          <t xml:space="preserve">Mon-2;Mon-3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE 3B</t>
+          <t xml:space="preserve">Dr. Neha Gupta</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2793,27 +2704,19 @@
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3rd Sem</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>60</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B1;B2</t>
+      <c r="C3">
+        <v>16</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS302;CS505</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE 5A</t>
+          <t xml:space="preserve">Prof. Amandeep Singh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2821,27 +2724,24 @@
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5th Sem</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>58</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS301;CS303</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1;A2</t>
+          <t xml:space="preserve">Sat-3;Sat-4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSE 5B</t>
+          <t xml:space="preserve">Ms. Priya Sharma</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2849,216 +2749,542 @@
           <t xml:space="preserve">CSE</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5th Sem</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>56</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B1;B2</t>
+      <c r="C5">
+        <v>18</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS302;CS304</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT 3A</t>
+          <t xml:space="preserve">Dr. Sandeep Bansal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3rd Sem</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>60</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS501;CS503</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1;A2</t>
+          <t xml:space="preserve">Fri-6;Fri-7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT 5A</t>
+          <t xml:space="preserve">Prof. Kavita Joshi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5th Sem</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>54</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A1;A2</t>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS502;CS505</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE 3A</t>
+          <t xml:space="preserve">Ms. Anjali Mehta</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3rd Sem</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>60</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A1;A2</t>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS501;CS503</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE 3B</t>
+          <t xml:space="preserve">Ms. Simran Kaur</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3rd Sem</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>58</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS303;CS304;CS504</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1;B2</t>
+          <t xml:space="preserve">Wed-2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE 5A</t>
+          <t xml:space="preserve">Mr. Rohit Verma</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5th Sem</t>
-        </is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>20</v>
       </c>
       <c r="D10">
-        <v>50</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A1;A2</t>
+        <v>6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS301;CS302;CS501;CS502;CS503</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME 3A</t>
+          <t xml:space="preserve">Dr. Harpreet Kaur</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3rd Sem</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>60</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT301;IT304</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1;A2</t>
+          <t xml:space="preserve">Wed-5;Wed-6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ME 5A</t>
+          <t xml:space="preserve">Prof. Manish Arora</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT302;IT501</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ms. Deepika Rana</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>18</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT303;IT503</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sat-1;Sat-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mr. Vivek Sood</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT302;IT502;IT504</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Sunil Mehra</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EC301;EC303</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tue-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prof. Ritu Malhotra</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EC302;EC304</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Gaurav Chawla</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EC501;EC503</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fri-1;Fri-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ms. Pallavi Sethi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>18</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EC502;EC504;EC303</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mr. Harish Thakur</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>20</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EC301;EC302;EC501;EC502</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Balwinder Singh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t xml:space="preserve">ME</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5th Sem</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>45</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A1;A2</t>
+      <c r="C20">
+        <v>16</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME301;ME503</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thu-6;Thu-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prof. Anil Saini</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME302;ME501</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sat-1;Sat-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mr. Jaspreet Gill</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>18</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME303;ME304</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Meenakshi Rao</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>16</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME502;ME504</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mr. Tarun Bedi</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>6</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME301;ME303;ME304;ME501;ME502</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Sunita Rani</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AS</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>18</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MA301</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sat-3;Sat-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Arvind Kapoor</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AS</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>18</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MA301</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mon-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ms. Nidhi Bhatia</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUM</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>14</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HU301;HU501</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thu-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mr. Karan Malik</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUM</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>14</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HU301;HU501</t>
         </is>
       </c>
     </row>
@@ -3072,6 +3298,391 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">department</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semester</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">students</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lab_groups</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group_names</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">max_per_day</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE 3A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3rd Sem</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>60</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1;A2</t>
+        </is>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE 3B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3rd Sem</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B1;B2</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE 5A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5th Sem</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>58</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1;A2</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE 5B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5th Sem</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>56</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B1;B2</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT 3A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3rd Sem</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1;A2</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT 5A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5th Sem</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>54</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1;A2</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE 3A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3rd Sem</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1;A2</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE 3B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3rd Sem</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>58</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B1;B2</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE 5A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5th Sem</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1;A2</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME 3A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3rd Sem</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>60</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1;A2</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME 5A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ME</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5th Sem</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>45</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1;A2</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t xml:space="preserve">section</t>
         </is>
       </c>
